--- a/策划/数据表.xlsx
+++ b/策划/数据表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -302,6 +302,9 @@
     <t>楼梯</t>
   </si>
   <si>
+    <t>最后5张</t>
+  </si>
+  <si>
     <t>特殊</t>
   </si>
   <si>
@@ -309,9 +312,6 @@
   </si>
   <si>
     <t>门</t>
-  </si>
-  <si>
-    <t>最后5张</t>
   </si>
   <si>
     <t>阻挡了前进的路</t>
@@ -2534,14 +2534,17 @@
       <c r="D33" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="G33" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2549,19 +2552,16 @@
         <v>90002</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="G34" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>92</v>
@@ -2578,7 +2578,7 @@
         <v>44</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>94</v>
@@ -2808,7 +2808,7 @@
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
     <col min="3" max="3" width="6.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="8.125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3473,8 +3473,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -3529,6 +3529,16 @@
       </c>
       <c r="C6" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/策划/数据表.xlsx
+++ b/策划/数据表.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具表" sheetId="1" r:id="R2fc7721f4a4e48be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件表" sheetId="2" r:id="Rb6a0acdf16eb4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff表" sheetId="3" r:id="R3291d43a013e4161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人表" sheetId="4" r:id="R1a959b560ecb4098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人技能表" sheetId="6" r:id="R954e570008b04825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="骰子表" sheetId="5" r:id="R1716ee1a82944d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强化类型表" sheetId="8" r:id="Rf9b5323556ed4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据表" sheetId="9" r:id="R0b1196463dd64818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励表" sheetId="10" r:id="R750c6e7171c84625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励项" sheetId="11" r:id="R721150c1ed654863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具表" sheetId="1" r:id="R01af376e75ea4de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件表" sheetId="2" r:id="R7d966097f9aa4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff表" sheetId="3" r:id="R3cf75461ae5543b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人表" sheetId="4" r:id="Rd9b739cd85b34df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人技能表" sheetId="6" r:id="Rb91e2a848521437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="骰子表" sheetId="5" r:id="R15b3275bd5084120"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强化类型表" sheetId="8" r:id="R3a5ece31dc3f4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据表" sheetId="9" r:id="R0608a1023a9a425f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励表" sheetId="10" r:id="R3654bf670cd54f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励项" sheetId="11" r:id="R78e01f154ee54880"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,9 +155,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">战斗</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">100 50 20 5</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2层测试战斗</x:t>
@@ -1647,7 +1644,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1655,7 +1652,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C2">
         <x:v>20</x:v>
@@ -1666,7 +1663,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C3">
         <x:v>30</x:v>
@@ -1775,6 +1772,1106 @@
     <x:row r="24">
       <x:c r="A24">
         <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>10002</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>10002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>10003</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>10003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>10004</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>10004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>10005</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>10005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>10006</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>10006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>10007</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>10007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>10008</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>10008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>10009</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>10009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>10010</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>10010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>10011</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>10011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>10012</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>10012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>10013</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>10013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>10014</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>10014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>10015</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>10015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>10016</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>10016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>10017</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>10017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>10018</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>10018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>10019</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C43" t="n">
+        <x:v>10019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>10020</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C44" t="n">
+        <x:v>10020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>10021</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C45" t="n">
+        <x:v>10021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>10022</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C46" t="n">
+        <x:v>10022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>10023</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C47" t="n">
+        <x:v>10023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>10024</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C48" t="n">
+        <x:v>10024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="n">
+        <x:v>10025</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C49" t="n">
+        <x:v>10025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="n">
+        <x:v>10026</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C50" t="n">
+        <x:v>10026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="n">
+        <x:v>10027</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C51" t="n">
+        <x:v>10027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="n">
+        <x:v>10028</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C52" t="n">
+        <x:v>10028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="n">
+        <x:v>10029</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C53" t="n">
+        <x:v>10029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="n">
+        <x:v>10030</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C54" t="n">
+        <x:v>10030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="n">
+        <x:v>10031</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C55" t="n">
+        <x:v>10031</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="n">
+        <x:v>10032</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C56" t="n">
+        <x:v>10032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="n">
+        <x:v>10033</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C57" t="n">
+        <x:v>10033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="n">
+        <x:v>10034</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C58" t="n">
+        <x:v>10034</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="n">
+        <x:v>10035</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C59" t="n">
+        <x:v>10035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="n">
+        <x:v>10036</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C60" t="n">
+        <x:v>10036</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="n">
+        <x:v>10037</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C61" t="n">
+        <x:v>10037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="n">
+        <x:v>10038</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C62" t="n">
+        <x:v>10038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="n">
+        <x:v>10039</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C63" t="n">
+        <x:v>10039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="n">
+        <x:v>10040</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C64" t="n">
+        <x:v>10040</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="n">
+        <x:v>10041</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C65" t="n">
+        <x:v>10041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="n">
+        <x:v>10042</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C66" t="n">
+        <x:v>10042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="n">
+        <x:v>10043</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C67" t="n">
+        <x:v>10043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="n">
+        <x:v>10044</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C68" t="n">
+        <x:v>10044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="n">
+        <x:v>10045</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C69" t="n">
+        <x:v>10045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="n">
+        <x:v>10046</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C70" t="n">
+        <x:v>10046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="n">
+        <x:v>10047</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C71" t="n">
+        <x:v>10047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="n">
+        <x:v>10048</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C72" t="n">
+        <x:v>10048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="n">
+        <x:v>10049</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C73" t="n">
+        <x:v>10049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="n">
+        <x:v>10050</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C74" t="n">
+        <x:v>10050</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="n">
+        <x:v>10051</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C75" t="n">
+        <x:v>10051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="n">
+        <x:v>10052</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C76" t="n">
+        <x:v>10052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="n">
+        <x:v>10053</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C77" t="n">
+        <x:v>10053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="n">
+        <x:v>10054</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C78" t="n">
+        <x:v>10054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="n">
+        <x:v>10055</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C79" t="n">
+        <x:v>10055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="n">
+        <x:v>10056</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C80" t="n">
+        <x:v>10056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="n">
+        <x:v>10057</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C81" t="n">
+        <x:v>10057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="n">
+        <x:v>10058</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C82" t="n">
+        <x:v>10058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="n">
+        <x:v>10059</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C83" t="n">
+        <x:v>10059</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="n">
+        <x:v>10060</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C84" t="n">
+        <x:v>10060</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="n">
+        <x:v>10061</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C85" t="n">
+        <x:v>10061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="n">
+        <x:v>10062</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C86" t="n">
+        <x:v>10062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="n">
+        <x:v>10063</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C87" t="n">
+        <x:v>10063</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="n">
+        <x:v>10064</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C88" t="n">
+        <x:v>10064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="n">
+        <x:v>10065</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C89" t="n">
+        <x:v>10065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="n">
+        <x:v>10066</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C90" t="n">
+        <x:v>10066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="n">
+        <x:v>10067</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C91" t="n">
+        <x:v>10067</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>10068</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C92" t="n">
+        <x:v>10068</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="n">
+        <x:v>10069</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C93" t="n">
+        <x:v>10069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="n">
+        <x:v>10070</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C94" t="n">
+        <x:v>10070</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="n">
+        <x:v>10071</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C95" t="n">
+        <x:v>10071</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="n">
+        <x:v>10072</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C96" t="n">
+        <x:v>10072</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="n">
+        <x:v>10073</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C97" t="n">
+        <x:v>10073</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>10074</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C98" t="n">
+        <x:v>10074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>10075</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C99" t="n">
+        <x:v>10075</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>10076</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C100" t="n">
+        <x:v>10076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C101" t="n">
+        <x:v>10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>10078</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C102" t="n">
+        <x:v>10078</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>10079</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C103" t="n">
+        <x:v>10079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>10080</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C104" t="n">
+        <x:v>10080</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>10081</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C105" t="n">
+        <x:v>10081</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>10082</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C106" t="n">
+        <x:v>10082</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>10083</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C107" t="n">
+        <x:v>10083</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>10084</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C108" t="n">
+        <x:v>10084</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="n">
+        <x:v>10085</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C109" t="n">
+        <x:v>10085</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="n">
+        <x:v>10086</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C110" t="n">
+        <x:v>10086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="n">
+        <x:v>10087</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C111" t="n">
+        <x:v>10087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="n">
+        <x:v>10088</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C112" t="n">
+        <x:v>10088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>10089</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C113" t="n">
+        <x:v>10089</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>10090</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C114" t="n">
+        <x:v>10090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>10091</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C115" t="n">
+        <x:v>10091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>10092</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C116" t="n">
+        <x:v>10092</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>10093</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C117" t="n">
+        <x:v>10093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>10094</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C118" t="n">
+        <x:v>10094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>10095</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C119" t="n">
+        <x:v>10095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>10096</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C120" t="n">
+        <x:v>10096</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>10097</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C121" t="n">
+        <x:v>10097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>10098</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C122" t="n">
+        <x:v>10098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>10099</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C123" t="n">
+        <x:v>10099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="n">
+        <x:v>10100</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>物品</x:v>
+      </x:c>
+      <x:c r="C124" t="n">
+        <x:v>10100</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1860,8 +2957,8 @@
       <x:c r="J2" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>46</x:v>
+      <x:c r="K2" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M2" t="str">
         <x:v>PathCard_BattleTest</x:v>
@@ -1872,7 +2969,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>43</x:v>
@@ -1881,19 +2978,19 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>46</x:v>
+      <x:c r="K3" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M3" t="str">
         <x:v>PathCard_BattleTest</x:v>
@@ -1904,7 +3001,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>43</x:v>
@@ -1913,19 +3010,19 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J4" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K4" s="1" t="s">
-        <x:v>46</x:v>
+      <x:c r="K4" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M4" t="str">
         <x:v>PathCard_BattleTest</x:v>
@@ -1939,13 +3036,13 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>44</x:v>
@@ -1957,13 +3054,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J6" s="1" t="s">
+      <x:c r="K6" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="K6" s="1" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="M6" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -1974,13 +3071,13 @@
         <x:v>20002</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>44</x:v>
@@ -1992,13 +3089,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J7" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K7" s="1" t="s">
-        <x:v>56</x:v>
+      <x:c r="K7" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M7" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -2009,31 +3106,31 @@
         <x:v>20003</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K8" s="1" t="s">
-        <x:v>56</x:v>
+      <x:c r="K8" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -2044,31 +3141,31 @@
         <x:v>20004</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K9" s="1" t="s">
-        <x:v>56</x:v>
+      <x:c r="K9" s="1" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M9" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -2079,28 +3176,31 @@
         <x:v>20005</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M10" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -2111,28 +3211,31 @@
         <x:v>20006</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>PathCard_Boss</x:v>
@@ -2143,13 +3246,13 @@
         <x:v>20007</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>44</x:v>
@@ -2158,13 +3261,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="J12" s="1" t="s">
+      <x:c r="K12" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
+      </x:c>
+      <x:c r="L12" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="L12" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="M12" t="str">
         <x:v>PathCard_Giant</x:v>
@@ -2175,13 +3281,13 @@
         <x:v>20008</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>44</x:v>
@@ -2190,13 +3296,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="J13" s="1" t="s">
+      <x:c r="K13" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
+      </x:c>
+      <x:c r="L13" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="L13" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>PathCard_Giant</x:v>
@@ -2222,7 +3331,7 @@
         <x:v>30001</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>43</x:v>
@@ -2231,13 +3340,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H19" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H19" s="1" t="s">
+      <x:c r="I19" s="1" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="I19" s="1" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="M19" t="str">
         <x:v>PathCard_PoisonSwamp</x:v>
@@ -2248,7 +3357,7 @@
         <x:v>30002</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>43</x:v>
@@ -2257,13 +3366,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H20" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>PathCard_CursedJungle</x:v>
@@ -2277,7 +3386,7 @@
         <x:v>40001</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>43</x:v>
@@ -2289,10 +3398,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I22" s="1" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>PathCard_MysteriousTraveler</x:v>
@@ -2303,7 +3412,7 @@
         <x:v>40002</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>43</x:v>
@@ -2312,13 +3421,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I23" s="1" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I23" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>PathCard_Mushroom</x:v>
@@ -2338,22 +3447,25 @@
         <x:v>50001</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H27" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="s">
+      <x:c r="I27" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="I27" s="1" t="s">
-        <x:v>82</x:v>
+      <x:c r="K27" t="str">
+        <x:v>2001 2002 2003 2004 2005 2006 2007 2008 2009 2010 2011 2012 2013 2014 2015 2016 2017 2018 2019 2020 2021 2022 2023 2024 2025 2026 2027 2028 2029 2030 2031 2032 2033 2034 2035 2036 2037 2038 2039 2040 2041 2042 2043 2044 2045 2046 2047 2048 2049 2050</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>PathCard_AbandonedAltar</x:v>
@@ -2364,22 +3476,22 @@
         <x:v>50002</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>PathCard_Altar</x:v>
@@ -2390,22 +3502,22 @@
         <x:v>50003</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>PathCard_CursedAltar</x:v>
@@ -2425,22 +3537,22 @@
         <x:v>90001</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
+      <x:c r="G33" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H33" s="1" t="s">
+      <x:c r="I33" s="1" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="I33" s="1" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>PathCard_Stairs</x:v>
@@ -2451,19 +3563,19 @@
         <x:v>90002</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H34" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I34" s="1" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G34" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H34" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="I34" s="1" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>PathCard_Door</x:v>
@@ -2477,19 +3589,19 @@
         <x:v>91001</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I36" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="L36" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="L36" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>PathCard_Altar</x:v>
@@ -2523,13 +3635,13 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C2" t="s">
+      <x:c r="D2" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2537,13 +3649,13 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="B7" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C7" t="s">
+      <x:c r="D7" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="D7" t="s">
-        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2551,13 +3663,13 @@
         <x:v>20002</x:v>
       </x:c>
       <x:c r="B8" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D8" t="s">
-        <x:v>103</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2583,13 +3695,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E1" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -2597,10 +3709,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="D2">
         <x:v>10</x:v>
@@ -2614,10 +3726,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D3">
         <x:v>10</x:v>
@@ -2631,10 +3743,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D4">
         <x:v>10</x:v>
@@ -2648,10 +3760,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D5">
         <x:v>10</x:v>
@@ -2665,16 +3777,16 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B8" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="D8">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F8" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2682,10 +3794,10 @@
         <x:v>9001</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D11">
         <x:v>999</x:v>
@@ -2717,13 +3829,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D1" t="s">
+      <x:c r="E1" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="F1" t="s">
         <x:v>8</x:v>
@@ -2734,7 +3846,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>1</x:v>
@@ -2751,7 +3863,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>1</x:v>
@@ -2763,7 +3875,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2771,7 +3883,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1</x:v>
@@ -2783,7 +3895,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2791,10 +3903,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D5">
         <x:v>1</x:v>
@@ -2808,10 +3920,10 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D7">
         <x:v>1</x:v>
@@ -2820,7 +3932,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2828,10 +3940,10 @@
         <x:v>9001</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D9">
         <x:v>1</x:v>
@@ -2840,7 +3952,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2866,7 +3978,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" customHeight="1">
@@ -2874,13 +3986,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D2" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -2888,13 +4000,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -2902,13 +4014,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D4" t="s">
-        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -2916,44 +4028,44 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1"/>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="B7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="C7" t="s">
+      <x:c r="D7" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="D7" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="B8" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D8" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="B9" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C9" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="C9" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D9" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1"/>
@@ -2961,36 +4073,36 @@
     <x:row r="12" ht="15" customHeight="1"/>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="B13" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C13" t="s">
+      <x:c r="D13" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="D13" t="s">
-        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="B14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" customHeight="1"/>
     <x:row r="16" ht="15" customHeight="1">
       <x:c r="B16" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="C16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D16" t="s">
-        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" customHeight="1"/>
@@ -2999,13 +4111,13 @@
         <x:v>9001</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C18" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="D18" t="s">
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1"/>
@@ -3035,7 +4147,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>38</x:v>
@@ -3046,240 +4158,240 @@
     </x:row>
     <x:row r="2">
       <x:c r="B2" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="B3" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="B16" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="B19" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="B23" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="B26" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3299,13 +4411,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C1" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3313,10 +4425,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="D2">
         <x:v>0</x:v>
@@ -3369,7 +4481,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3402,7 +4514,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3413,7 +4525,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3424,6 +4536,556 @@
     <x:row r="10">
       <x:c r="B10">
         <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>10001 10002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="n">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>10003 10004 10005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="n">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>10005 10006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="n">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>10007 10008 10009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="n">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>10009 10010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="n">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>10011 10012 10013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>10013 10014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>10015 10016 10017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>10017 10018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="B20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>10019 10020 10021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>10021 10022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>10023 10024 10025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>10025 10026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>10027 10028 10029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>10029 10030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>10031 10032 10033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>10033 10034</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>10035 10036 10037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>10037 10038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>10039 10040 10041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>10041 10042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>10043 10044 10045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>10045 10046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>10047 10048 10049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>10049 10050</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>10051 10052 10053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>10053 10054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>10055 10056 10057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>10057 10058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>10059 10060 10061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>10061 10062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>2032</x:v>
+      </x:c>
+      <x:c r="B42" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>10063 10064 10065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>2033</x:v>
+      </x:c>
+      <x:c r="B43" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>10065 10066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>2034</x:v>
+      </x:c>
+      <x:c r="B44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>10067 10068 10069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>2035</x:v>
+      </x:c>
+      <x:c r="B45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>10069 10070</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>2036</x:v>
+      </x:c>
+      <x:c r="B46" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>10071 10072 10073</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>2037</x:v>
+      </x:c>
+      <x:c r="B47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>10073 10074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>2038</x:v>
+      </x:c>
+      <x:c r="B48" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>10075 10076 10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="n">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="B49" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>10077 10078</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="n">
+        <x:v>2040</x:v>
+      </x:c>
+      <x:c r="B50" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>10079 10080 10081</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="n">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="B51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>10081 10082</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="n">
+        <x:v>2042</x:v>
+      </x:c>
+      <x:c r="B52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>10083 10084 10085</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="n">
+        <x:v>2043</x:v>
+      </x:c>
+      <x:c r="B53" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>10085 10086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="n">
+        <x:v>2044</x:v>
+      </x:c>
+      <x:c r="B54" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>10087 10088 10089</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="n">
+        <x:v>2045</x:v>
+      </x:c>
+      <x:c r="B55" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>10089 10090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="n">
+        <x:v>2046</x:v>
+      </x:c>
+      <x:c r="B56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>10091 10092 10093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="n">
+        <x:v>2047</x:v>
+      </x:c>
+      <x:c r="B57" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>10093 10094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="n">
+        <x:v>2048</x:v>
+      </x:c>
+      <x:c r="B58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>10095 10096 10097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="n">
+        <x:v>2049</x:v>
+      </x:c>
+      <x:c r="B59" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>10097 10098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="n">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="B60" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>10099 10100 10001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
